--- a/Avaliações dos Itens/Avaliações (2008-2024)/2020 nível junior tipo A.xlsx
+++ b/Avaliações dos Itens/Avaliações (2008-2024)/2020 nível junior tipo A.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/criterios por questoes e provas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{CE45B94B-5053-4CF3-9D1E-DD466CC80074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8ED36C88-6693-4506-95AB-8FC4615A2AED}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{CE45B94B-5053-4CF3-9D1E-DD466CC80074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{884AAA8A-EA41-44FF-9C59-97CA4E4EE0D5}"/>
   <bookViews>
     <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" xr2:uid="{C6A9867F-6A92-41FD-A04A-6522B6A56F0D}"/>
   </bookViews>
@@ -151,10 +146,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,30 +648,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
-    </row>
-    <row r="78" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-    </row>
-    <row r="79" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2"/>
-    </row>
-    <row r="82" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
-    </row>
-    <row r="83" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="2"/>
-    </row>
-    <row r="88" spans="1:1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="2"/>
-    </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="1"/>
-    </row>
+    <row r="17" x14ac:dyDescent="0.3"/>
+    <row r="18" x14ac:dyDescent="0.3"/>
+    <row r="19" x14ac:dyDescent="0.3"/>
+    <row r="20" x14ac:dyDescent="0.3"/>
+    <row r="21" x14ac:dyDescent="0.3"/>
+    <row r="22" x14ac:dyDescent="0.3"/>
+    <row r="23" x14ac:dyDescent="0.3"/>
+    <row r="24" x14ac:dyDescent="0.3"/>
+    <row r="25" x14ac:dyDescent="0.3"/>
+    <row r="26" x14ac:dyDescent="0.3"/>
+    <row r="27" x14ac:dyDescent="0.3"/>
+    <row r="28" x14ac:dyDescent="0.3"/>
+    <row r="29" x14ac:dyDescent="0.3"/>
+    <row r="30" x14ac:dyDescent="0.3"/>
+    <row r="31" x14ac:dyDescent="0.3"/>
+    <row r="32" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
+    <row r="35" x14ac:dyDescent="0.3"/>
+    <row r="36" x14ac:dyDescent="0.3"/>
+    <row r="37" x14ac:dyDescent="0.3"/>
+    <row r="38" x14ac:dyDescent="0.3"/>
+    <row r="39" x14ac:dyDescent="0.3"/>
+    <row r="40" x14ac:dyDescent="0.3"/>
+    <row r="41" x14ac:dyDescent="0.3"/>
+    <row r="42" x14ac:dyDescent="0.3"/>
+    <row r="43" x14ac:dyDescent="0.3"/>
+    <row r="44" x14ac:dyDescent="0.3"/>
+    <row r="45" x14ac:dyDescent="0.3"/>
+    <row r="46" x14ac:dyDescent="0.3"/>
+    <row r="47" x14ac:dyDescent="0.3"/>
+    <row r="48" x14ac:dyDescent="0.3"/>
+    <row r="49" x14ac:dyDescent="0.3"/>
+    <row r="50" x14ac:dyDescent="0.3"/>
+    <row r="51" x14ac:dyDescent="0.3"/>
+    <row r="52" x14ac:dyDescent="0.3"/>
+    <row r="53" x14ac:dyDescent="0.3"/>
+    <row r="54" x14ac:dyDescent="0.3"/>
+    <row r="55" x14ac:dyDescent="0.3"/>
+    <row r="56" x14ac:dyDescent="0.3"/>
+    <row r="57" x14ac:dyDescent="0.3"/>
+    <row r="58" x14ac:dyDescent="0.3"/>
+    <row r="59" x14ac:dyDescent="0.3"/>
+    <row r="60" x14ac:dyDescent="0.3"/>
+    <row r="61" x14ac:dyDescent="0.3"/>
+    <row r="62" x14ac:dyDescent="0.3"/>
+    <row r="63" x14ac:dyDescent="0.3"/>
+    <row r="64" x14ac:dyDescent="0.3"/>
+    <row r="65" x14ac:dyDescent="0.3"/>
+    <row r="66" x14ac:dyDescent="0.3"/>
+    <row r="67" x14ac:dyDescent="0.3"/>
+    <row r="68" x14ac:dyDescent="0.3"/>
+    <row r="69" x14ac:dyDescent="0.3"/>
+    <row r="70" x14ac:dyDescent="0.3"/>
+    <row r="71" x14ac:dyDescent="0.3"/>
+    <row r="72" x14ac:dyDescent="0.3"/>
+    <row r="73" x14ac:dyDescent="0.3"/>
+    <row r="74" x14ac:dyDescent="0.3"/>
+    <row r="75" x14ac:dyDescent="0.3"/>
+    <row r="76" x14ac:dyDescent="0.3"/>
+    <row r="77" x14ac:dyDescent="0.3"/>
+    <row r="78" x14ac:dyDescent="0.3"/>
+    <row r="79" x14ac:dyDescent="0.3"/>
+    <row r="80" x14ac:dyDescent="0.3"/>
+    <row r="81" x14ac:dyDescent="0.3"/>
+    <row r="82" x14ac:dyDescent="0.3"/>
+    <row r="83" x14ac:dyDescent="0.3"/>
+    <row r="84" x14ac:dyDescent="0.3"/>
+    <row r="85" x14ac:dyDescent="0.3"/>
+    <row r="86" x14ac:dyDescent="0.3"/>
+    <row r="87" x14ac:dyDescent="0.3"/>
+    <row r="88" x14ac:dyDescent="0.3"/>
+    <row r="89" x14ac:dyDescent="0.3"/>
+    <row r="90" x14ac:dyDescent="0.3"/>
+    <row r="91" x14ac:dyDescent="0.3"/>
+    <row r="92" x14ac:dyDescent="0.3"/>
+    <row r="93" x14ac:dyDescent="0.3"/>
+    <row r="94" x14ac:dyDescent="0.3"/>
+    <row r="95" x14ac:dyDescent="0.3"/>
+    <row r="96" x14ac:dyDescent="0.3"/>
+    <row r="97" x14ac:dyDescent="0.3"/>
+    <row r="98" x14ac:dyDescent="0.3"/>
+    <row r="99" x14ac:dyDescent="0.3"/>
+    <row r="100" x14ac:dyDescent="0.3"/>
+    <row r="101" x14ac:dyDescent="0.3"/>
+    <row r="102" x14ac:dyDescent="0.3"/>
+    <row r="103" x14ac:dyDescent="0.3"/>
+    <row r="104" x14ac:dyDescent="0.3"/>
+    <row r="105" x14ac:dyDescent="0.3"/>
+    <row r="106" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>